--- a/Sample_Data/Employees.xlsx
+++ b/Sample_Data/Employees.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="140">
   <si>
     <t>employee_ID INT (PK)</t>
   </si>
@@ -248,6 +248,189 @@
   </si>
   <si>
     <t>Unit Coordinator</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>General Surgeon</t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t>Strange</t>
+  </si>
+  <si>
+    <t>Neurosurgeon</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>Emergency Physician</t>
+  </si>
+  <si>
+    <t>Claire</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>Night Nurse</t>
+  </si>
+  <si>
+    <t>Leonard</t>
+  </si>
+  <si>
+    <t>McCoy</t>
+  </si>
+  <si>
+    <t>Chief Medical Officer</t>
+  </si>
+  <si>
+    <t>Beverly</t>
+  </si>
+  <si>
+    <t>Crusher</t>
+  </si>
+  <si>
+    <t>Head of Medical</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t>Bashir</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Tam</t>
+  </si>
+  <si>
+    <t>Trauma Surgeon</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>Griffin</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Avery</t>
+  </si>
+  <si>
+    <t>Plastic Surgeon</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Kepner</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Webber</t>
+  </si>
+  <si>
+    <t>Chief of Surgery</t>
+  </si>
+  <si>
+    <t>Owen</t>
+  </si>
+  <si>
+    <t>Hunt</t>
+  </si>
+  <si>
+    <t>Head of Trauma</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Robbins</t>
+  </si>
+  <si>
+    <t>Pediatric Surgeon</t>
+  </si>
+  <si>
+    <t>Callie</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Orthopedic Surgeon</t>
+  </si>
+  <si>
+    <t>Lexie</t>
+  </si>
+  <si>
+    <t>Surgical Resident</t>
+  </si>
+  <si>
+    <t>Sloan</t>
+  </si>
+  <si>
+    <t>Addison</t>
+  </si>
+  <si>
+    <t>Montgomery</t>
+  </si>
+  <si>
+    <t>Neonatal Surgeon</t>
+  </si>
+  <si>
+    <t>Amelia</t>
+  </si>
+  <si>
+    <t>Maggie</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>Cardiothoracic Surgeon</t>
+  </si>
+  <si>
+    <t>Jo</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Karev</t>
+  </si>
+  <si>
+    <t>Stephanie</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Warren</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>DeLuca</t>
   </si>
 </sst>
 </file>
@@ -963,6 +1146,431 @@
         <v>4.0</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>126.0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>127.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>128.0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>129.0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>130.0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>131.0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>132.0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>133.0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>134.0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>135.0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>136.0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>137.0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>138.0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>139.0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>140.0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>141.0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>142.0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>143.0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>144.0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>145.0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>146.0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>147.0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>148.0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>149.0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
